--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/136.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/136.xlsx
@@ -426,13 +426,13 @@
         <v>-18.19706260703381</v>
       </c>
       <c r="E2">
-        <v>-15.29672084179528</v>
+        <v>-26.14233910610766</v>
       </c>
       <c r="F2">
-        <v>-2.279974564058186</v>
+        <v>-5.007651740855496</v>
       </c>
       <c r="G2">
-        <v>-12.92025174864101</v>
+        <v>-19.13249173110169</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.61273257325542</v>
       </c>
       <c r="E3">
-        <v>-15.22671969058471</v>
+        <v>-26.19164513110317</v>
       </c>
       <c r="F3">
-        <v>-2.528844296350853</v>
+        <v>-4.717264234334518</v>
       </c>
       <c r="G3">
-        <v>-12.69435605038104</v>
+        <v>-18.08739805525685</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.90663649545273</v>
       </c>
       <c r="E4">
-        <v>-16.37898084488842</v>
+        <v>-26.49204145440198</v>
       </c>
       <c r="F4">
-        <v>-2.254073172107451</v>
+        <v>-4.799898852968186</v>
       </c>
       <c r="G4">
-        <v>-12.96295684723718</v>
+        <v>-18.4901105803014</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.1360669070737</v>
       </c>
       <c r="E5">
-        <v>-16.76469814696575</v>
+        <v>-27.01712707253938</v>
       </c>
       <c r="F5">
-        <v>-2.211899330896122</v>
+        <v>-5.023292145787753</v>
       </c>
       <c r="G5">
-        <v>-12.39178804794152</v>
+        <v>-18.22799347724672</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.30968057557456</v>
       </c>
       <c r="E6">
-        <v>-17.97986433371</v>
+        <v>-28.31718856150543</v>
       </c>
       <c r="F6">
-        <v>-2.22281721326502</v>
+        <v>-4.736954527499062</v>
       </c>
       <c r="G6">
-        <v>-11.49072851428085</v>
+        <v>-17.93289517568727</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.46616663207259</v>
       </c>
       <c r="E7">
-        <v>-18.52763307815182</v>
+        <v>-30.35922240273224</v>
       </c>
       <c r="F7">
-        <v>-2.118428838266435</v>
+        <v>-4.803879158338638</v>
       </c>
       <c r="G7">
-        <v>-11.38071571783579</v>
+        <v>-17.53688782689945</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.62065463827751</v>
       </c>
       <c r="E8">
-        <v>-18.91239940068754</v>
+        <v>-29.77050719631307</v>
       </c>
       <c r="F8">
-        <v>-1.93892410718199</v>
+        <v>-4.704540511027518</v>
       </c>
       <c r="G8">
-        <v>-11.29175852013768</v>
+        <v>-17.9356120271385</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.78966141558107</v>
       </c>
       <c r="E9">
-        <v>-19.5327550549983</v>
+        <v>-29.41031690221698</v>
       </c>
       <c r="F9">
-        <v>-1.859163923436037</v>
+        <v>-4.63852956943323</v>
       </c>
       <c r="G9">
-        <v>-10.46604239592498</v>
+        <v>-17.78422630805039</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.99335479612266</v>
       </c>
       <c r="E10">
-        <v>-20.28615727565442</v>
+        <v>-30.76854663981155</v>
       </c>
       <c r="F10">
-        <v>-1.964440308290423</v>
+        <v>-4.718091773369915</v>
       </c>
       <c r="G10">
-        <v>-9.916217942873505</v>
+        <v>-16.77385779996916</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.24057410191937</v>
       </c>
       <c r="E11">
-        <v>-20.95934210773866</v>
+        <v>-31.31378623152008</v>
       </c>
       <c r="F11">
-        <v>-1.766743800673099</v>
+        <v>-4.445428015799235</v>
       </c>
       <c r="G11">
-        <v>-9.745371298716337</v>
+        <v>-17.03761715441434</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.53652977436889</v>
       </c>
       <c r="E12">
-        <v>-21.64414700412659</v>
+        <v>-31.99848923724284</v>
       </c>
       <c r="F12">
-        <v>-1.683117626258281</v>
+        <v>-4.711362116589571</v>
       </c>
       <c r="G12">
-        <v>-9.05216730718181</v>
+        <v>-17.49419913441108</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.876745357018638</v>
       </c>
       <c r="E13">
-        <v>-22.16136213443865</v>
+        <v>-31.74782914397027</v>
       </c>
       <c r="F13">
-        <v>-1.772304631048092</v>
+        <v>-4.5375896879325</v>
       </c>
       <c r="G13">
-        <v>-8.116658228368525</v>
+        <v>-16.36017122941905</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.277940643187343</v>
       </c>
       <c r="E14">
-        <v>-23.97001653920616</v>
+        <v>-32.61590591192262</v>
       </c>
       <c r="F14">
-        <v>-1.481272654687736</v>
+        <v>-4.449253416465363</v>
       </c>
       <c r="G14">
-        <v>-8.192693975565538</v>
+        <v>-15.10514992003328</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.738459695652365</v>
       </c>
       <c r="E15">
-        <v>-24.13026564891559</v>
+        <v>-33.21821106883881</v>
       </c>
       <c r="F15">
-        <v>-1.452551500097872</v>
+        <v>-3.930213312484443</v>
       </c>
       <c r="G15">
-        <v>-7.751176083748216</v>
+        <v>-15.71284527772868</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.255576829331121</v>
       </c>
       <c r="E16">
-        <v>-24.9803689035315</v>
+        <v>-34.59762953631528</v>
       </c>
       <c r="F16">
-        <v>-1.516459216856451</v>
+        <v>-4.30843758492867</v>
       </c>
       <c r="G16">
-        <v>-7.042799723722816</v>
+        <v>-14.86801767854299</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.828380818727499</v>
       </c>
       <c r="E17">
-        <v>-25.31870478206658</v>
+        <v>-34.5443860031701</v>
       </c>
       <c r="F17">
-        <v>-1.133582833078102</v>
+        <v>-4.044991899816343</v>
       </c>
       <c r="G17">
-        <v>-6.659372578393904</v>
+        <v>-14.75853972121211</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.453200663981212</v>
       </c>
       <c r="E18">
-        <v>-26.77645226445372</v>
+        <v>-35.80467843340079</v>
       </c>
       <c r="F18">
-        <v>-1.146108576575834</v>
+        <v>-3.920614191020803</v>
       </c>
       <c r="G18">
-        <v>-6.082517422135726</v>
+        <v>-14.79768141319473</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.120327768883531</v>
       </c>
       <c r="E19">
-        <v>-27.82740692673183</v>
+        <v>-35.30446093027651</v>
       </c>
       <c r="F19">
-        <v>-1.041630737897746</v>
+        <v>-3.944131541586281</v>
       </c>
       <c r="G19">
-        <v>-6.189419620542434</v>
+        <v>-14.08513954239961</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.817330176586909</v>
       </c>
       <c r="E20">
-        <v>-27.86235316064903</v>
+        <v>-36.7696713378283</v>
       </c>
       <c r="F20">
-        <v>-0.9170235713316305</v>
+        <v>-3.663437590412863</v>
       </c>
       <c r="G20">
-        <v>-5.80635997202818</v>
+        <v>-13.74589240475784</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.544714388806018</v>
       </c>
       <c r="E21">
-        <v>-28.61324207823089</v>
+        <v>-37.11109110716259</v>
       </c>
       <c r="F21">
-        <v>-0.9333357822275583</v>
+        <v>-3.495675795630504</v>
       </c>
       <c r="G21">
-        <v>-5.643122480667365</v>
+        <v>-13.05108061465919</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.293400265206758</v>
       </c>
       <c r="E22">
-        <v>-28.53771166025695</v>
+        <v>-37.76888139185777</v>
       </c>
       <c r="F22">
-        <v>-0.7051421003087673</v>
+        <v>-3.68112571956484</v>
       </c>
       <c r="G22">
-        <v>-5.15080799788828</v>
+        <v>-13.22059180164166</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.057478079984167</v>
       </c>
       <c r="E23">
-        <v>-29.69972261909917</v>
+        <v>-38.57329234373628</v>
       </c>
       <c r="F23">
-        <v>-0.5425294373022104</v>
+        <v>-3.333548555921988</v>
       </c>
       <c r="G23">
-        <v>-4.850842004145403</v>
+        <v>-13.21370123636683</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.831438161005988</v>
       </c>
       <c r="E24">
-        <v>-30.17448104135232</v>
+        <v>-37.7151148199647</v>
       </c>
       <c r="F24">
-        <v>-0.5382542331363621</v>
+        <v>-3.500829897610723</v>
       </c>
       <c r="G24">
-        <v>-4.730608202542671</v>
+        <v>-13.280775967485</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.617800867260335</v>
       </c>
       <c r="E25">
-        <v>-29.95930380616685</v>
+        <v>-37.9642057969936</v>
       </c>
       <c r="F25">
-        <v>-0.3485738368759285</v>
+        <v>-3.178074763192757</v>
       </c>
       <c r="G25">
-        <v>-5.165796617971823</v>
+        <v>-12.79788187180308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.414413701977139</v>
       </c>
       <c r="E26">
-        <v>-30.04659919961271</v>
+        <v>-38.92451852353419</v>
       </c>
       <c r="F26">
-        <v>-0.3991050768141012</v>
+        <v>-3.280398846623565</v>
       </c>
       <c r="G26">
-        <v>-5.075067560631617</v>
+        <v>-12.78236497504846</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.220473019584619</v>
       </c>
       <c r="E27">
-        <v>-29.77644402573712</v>
+        <v>-37.80247814052067</v>
       </c>
       <c r="F27">
-        <v>-0.3234726478362979</v>
+        <v>-3.194374548577643</v>
       </c>
       <c r="G27">
-        <v>-4.887568717060268</v>
+        <v>-13.01657856996163</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.040794034422288</v>
       </c>
       <c r="E28">
-        <v>-30.45749028869869</v>
+        <v>-39.00996177111092</v>
       </c>
       <c r="F28">
-        <v>-0.3593682925018089</v>
+        <v>-3.067521677982537</v>
       </c>
       <c r="G28">
-        <v>-4.913838176865182</v>
+        <v>-13.22766939654538</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.875998163236477</v>
       </c>
       <c r="E29">
-        <v>-30.09419346143333</v>
+        <v>-38.17246352389535</v>
       </c>
       <c r="F29">
-        <v>-0.5376064498273729</v>
+        <v>-3.415944604743649</v>
       </c>
       <c r="G29">
-        <v>-5.129690055931693</v>
+        <v>-14.10444953127695</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.728596015423578</v>
       </c>
       <c r="E30">
-        <v>-29.58719909695658</v>
+        <v>-38.25178201037671</v>
       </c>
       <c r="F30">
-        <v>-0.2157658330220978</v>
+        <v>-3.448115909566173</v>
       </c>
       <c r="G30">
-        <v>-5.370892652766474</v>
+        <v>-13.66979759557276</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.597482269516272</v>
       </c>
       <c r="E31">
-        <v>-29.63378124483648</v>
+        <v>-38.80235614446627</v>
       </c>
       <c r="F31">
-        <v>-0.4313186283741683</v>
+        <v>-3.151572804874992</v>
       </c>
       <c r="G31">
-        <v>-5.383846915483162</v>
+        <v>-13.54968848038929</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.487915663183812</v>
       </c>
       <c r="E32">
-        <v>-28.52690219280064</v>
+        <v>-37.70954026846125</v>
       </c>
       <c r="F32">
-        <v>-0.3746723802685297</v>
+        <v>-3.073179427343658</v>
       </c>
       <c r="G32">
-        <v>-5.448355731341845</v>
+        <v>-13.1207409483662</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.396534912916916</v>
       </c>
       <c r="E33">
-        <v>-28.5282380926329</v>
+        <v>-37.91809687464751</v>
       </c>
       <c r="F33">
-        <v>-0.4582372554955411</v>
+        <v>-3.09307018541968</v>
       </c>
       <c r="G33">
-        <v>-5.6179817610789</v>
+        <v>-14.08654718644862</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.321934366419994</v>
       </c>
       <c r="E34">
-        <v>-28.30997923088522</v>
+        <v>-37.22413540381607</v>
       </c>
       <c r="F34">
-        <v>-0.3554169799904552</v>
+        <v>-3.63475536909093</v>
       </c>
       <c r="G34">
-        <v>-5.44454623311133</v>
+        <v>-14.4461247728727</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.26407577466229</v>
       </c>
       <c r="E35">
-        <v>-27.71932130911676</v>
+        <v>-36.73486095813134</v>
       </c>
       <c r="F35">
-        <v>-0.4236288937739805</v>
+        <v>-3.521185369799715</v>
       </c>
       <c r="G35">
-        <v>-6.190020084087813</v>
+        <v>-13.8922086365366</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.222848894085073</v>
       </c>
       <c r="E36">
-        <v>-27.13762070893547</v>
+        <v>-36.49373330264491</v>
       </c>
       <c r="F36">
-        <v>-0.3277685611872161</v>
+        <v>-3.255087252263624</v>
       </c>
       <c r="G36">
-        <v>-5.974627576039624</v>
+        <v>-14.02077510028955</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.198556780504807</v>
       </c>
       <c r="E37">
-        <v>-27.55585698286188</v>
+        <v>-36.72372996902048</v>
       </c>
       <c r="F37">
-        <v>-0.2785453133780639</v>
+        <v>-3.201879557247006</v>
       </c>
       <c r="G37">
-        <v>-6.214658776777683</v>
+        <v>-14.26264214449012</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.192462341395037</v>
       </c>
       <c r="E38">
-        <v>-26.41692312756275</v>
+        <v>-35.66838495119193</v>
       </c>
       <c r="F38">
-        <v>-0.2791922683196503</v>
+        <v>-3.400996714960132</v>
       </c>
       <c r="G38">
-        <v>-6.227606477051252</v>
+        <v>-14.21801753128167</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.210825142699957</v>
       </c>
       <c r="E39">
-        <v>-25.81149785205528</v>
+        <v>-34.98083806379236</v>
       </c>
       <c r="F39">
-        <v>-0.3774432692308941</v>
+        <v>-3.654940197594945</v>
       </c>
       <c r="G39">
-        <v>-6.748483993505303</v>
+        <v>-14.05467668144173</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.253432142682158</v>
       </c>
       <c r="E40">
-        <v>-25.55014150317659</v>
+        <v>-35.59236545802517</v>
       </c>
       <c r="F40">
-        <v>-0.1481503437685881</v>
+        <v>-3.212529876944799</v>
       </c>
       <c r="G40">
-        <v>-7.038967256941385</v>
+        <v>-14.22834189491846</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.32617314723262</v>
       </c>
       <c r="E41">
-        <v>-24.40852679126491</v>
+        <v>-34.20303868941992</v>
       </c>
       <c r="F41">
-        <v>0.04139254350298074</v>
+        <v>-3.027069184234227</v>
       </c>
       <c r="G41">
-        <v>-6.999267757293663</v>
+        <v>-14.61697141702987</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.432588499622466</v>
       </c>
       <c r="E42">
-        <v>-23.8254540634593</v>
+        <v>-34.73991418963628</v>
       </c>
       <c r="F42">
-        <v>-0.1987751892232771</v>
+        <v>-3.266021701980578</v>
       </c>
       <c r="G42">
-        <v>-7.165842250980433</v>
+        <v>-14.39363835280783</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.576641753844533</v>
       </c>
       <c r="E43">
-        <v>-23.43668909837481</v>
+        <v>-34.05145028625016</v>
       </c>
       <c r="F43">
-        <v>-0.259973316207299</v>
+        <v>-3.087216941351498</v>
       </c>
       <c r="G43">
-        <v>-7.526284439285435</v>
+        <v>-15.04031954446177</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.757728986536399</v>
       </c>
       <c r="E44">
-        <v>-22.79641721537831</v>
+        <v>-33.63484879144051</v>
       </c>
       <c r="F44">
-        <v>0.1407005412201967</v>
+        <v>-3.192205882717114</v>
       </c>
       <c r="G44">
-        <v>-7.521149327544904</v>
+        <v>-15.15514753354532</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.977333724354942</v>
       </c>
       <c r="E45">
-        <v>-21.92130319881804</v>
+        <v>-32.6829046848661</v>
       </c>
       <c r="F45">
-        <v>0.05963650718223706</v>
+        <v>-3.186642567239912</v>
       </c>
       <c r="G45">
-        <v>-7.36405756416493</v>
+        <v>-14.60375137536687</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.236257531451563</v>
       </c>
       <c r="E46">
-        <v>-21.16749794397524</v>
+        <v>-32.2643785886032</v>
       </c>
       <c r="F46">
-        <v>-0.08991860045399129</v>
+        <v>-3.018363871198206</v>
       </c>
       <c r="G46">
-        <v>-7.599514742049123</v>
+        <v>-14.75077799161325</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.526535786843964</v>
       </c>
       <c r="E47">
-        <v>-20.61545884854419</v>
+        <v>-32.75476930313083</v>
       </c>
       <c r="F47">
-        <v>0.162286967369749</v>
+        <v>-3.253783401971618</v>
       </c>
       <c r="G47">
-        <v>-7.673443945004972</v>
+        <v>-14.94025705239572</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.846065536597109</v>
       </c>
       <c r="E48">
-        <v>-20.00485752724595</v>
+        <v>-32.13967799985399</v>
       </c>
       <c r="F48">
-        <v>0.1238374660014071</v>
+        <v>-2.811714368691425</v>
       </c>
       <c r="G48">
-        <v>-7.734126856525342</v>
+        <v>-15.27827045073114</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.189204697955025</v>
       </c>
       <c r="E49">
-        <v>-19.65872814494367</v>
+        <v>-31.39254771569849</v>
       </c>
       <c r="F49">
-        <v>0.1434242132406015</v>
+        <v>-2.969224288496737</v>
       </c>
       <c r="G49">
-        <v>-8.393147081853575</v>
+        <v>-15.3412272487922</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.551740157671349</v>
       </c>
       <c r="E50">
-        <v>-19.25697098793118</v>
+        <v>-30.48997529699271</v>
       </c>
       <c r="F50">
-        <v>0.2737678240711037</v>
+        <v>-2.832546980504429</v>
       </c>
       <c r="G50">
-        <v>-8.297840720437945</v>
+        <v>-15.66108400762844</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.922097784023379</v>
       </c>
       <c r="E51">
-        <v>-18.66194308874531</v>
+        <v>-30.11385383133763</v>
       </c>
       <c r="F51">
-        <v>0.2786054897034528</v>
+        <v>-2.920325760709482</v>
       </c>
       <c r="G51">
-        <v>-9.12613916601793</v>
+        <v>-15.45280846914268</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.297236067104279</v>
       </c>
       <c r="E52">
-        <v>-17.8927229083804</v>
+        <v>-29.98273865915655</v>
       </c>
       <c r="F52">
-        <v>0.3229264592228375</v>
+        <v>-2.662317479229131</v>
       </c>
       <c r="G52">
-        <v>-8.902875007448634</v>
+        <v>-15.76209805394672</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.672027116044108</v>
       </c>
       <c r="E53">
-        <v>-17.42475493290176</v>
+        <v>-30.2340395315012</v>
       </c>
       <c r="F53">
-        <v>0.007405457333519828</v>
+        <v>-2.79899810069105</v>
       </c>
       <c r="G53">
-        <v>-9.037483840703294</v>
+        <v>-15.9091164671392</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.037408818915873</v>
       </c>
       <c r="E54">
-        <v>-17.33272275564387</v>
+        <v>-28.79334854646395</v>
       </c>
       <c r="F54">
-        <v>0.2384578351593719</v>
+        <v>-3.103891977169853</v>
       </c>
       <c r="G54">
-        <v>-9.258247708444294</v>
+        <v>-15.97689994211421</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.386566114199994</v>
       </c>
       <c r="E55">
-        <v>-16.69404036702407</v>
+        <v>-29.3486345577585</v>
       </c>
       <c r="F55">
-        <v>0.1137206149110168</v>
+        <v>-2.974874582551232</v>
       </c>
       <c r="G55">
-        <v>-9.603520809479983</v>
+        <v>-16.44802101484084</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.714753661645624</v>
       </c>
       <c r="E56">
-        <v>-16.42144887413235</v>
+        <v>-28.38174648695878</v>
       </c>
       <c r="F56">
-        <v>0.1863286745011991</v>
+        <v>-3.068282119258307</v>
       </c>
       <c r="G56">
-        <v>-9.384135054793949</v>
+        <v>-15.57372148360822</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.020024602972732</v>
       </c>
       <c r="E57">
-        <v>-15.77694286793868</v>
+        <v>-28.37821427723279</v>
       </c>
       <c r="F57">
-        <v>0.05758878296251668</v>
+        <v>-2.990181983787565</v>
       </c>
       <c r="G57">
-        <v>-9.869175069375746</v>
+        <v>-15.57758840321603</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.291450103374018</v>
       </c>
       <c r="E58">
-        <v>-15.78863085935248</v>
+        <v>-28.26543716054577</v>
       </c>
       <c r="F58">
-        <v>0.1654264798263591</v>
+        <v>-2.984551570550736</v>
       </c>
       <c r="G58">
-        <v>-9.958329140367418</v>
+        <v>-16.44105662208092</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.529706300161545</v>
       </c>
       <c r="E59">
-        <v>-14.88665846345271</v>
+        <v>-27.2075403476139</v>
       </c>
       <c r="F59">
-        <v>0.3007709446675619</v>
+        <v>-2.906241029759682</v>
       </c>
       <c r="G59">
-        <v>-9.98963527526608</v>
+        <v>-16.61633127473256</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.731374532402121</v>
       </c>
       <c r="E60">
-        <v>-14.34002636598682</v>
+        <v>-26.95277745689038</v>
       </c>
       <c r="F60">
-        <v>0.259524874947369</v>
+        <v>-3.234173460445145</v>
       </c>
       <c r="G60">
-        <v>-10.21078960837265</v>
+        <v>-15.40267468493593</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.896650997259355</v>
       </c>
       <c r="E61">
-        <v>-14.43341708544701</v>
+        <v>-27.1074701289924</v>
       </c>
       <c r="F61">
-        <v>0.04797889272263961</v>
+        <v>-3.25163296019395</v>
       </c>
       <c r="G61">
-        <v>-10.54127424383993</v>
+        <v>-15.94357585595649</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.02190410278494</v>
       </c>
       <c r="E62">
-        <v>-13.7902424506116</v>
+        <v>-26.96342389928241</v>
       </c>
       <c r="F62">
-        <v>0.2335704674828548</v>
+        <v>-2.957192251971074</v>
       </c>
       <c r="G62">
-        <v>-11.06367752831912</v>
+        <v>-16.59090180764686</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.1094385679867</v>
       </c>
       <c r="E63">
-        <v>-14.32715644285702</v>
+        <v>-26.29186478936692</v>
       </c>
       <c r="F63">
-        <v>-0.04814071886120102</v>
+        <v>-3.010221019628687</v>
       </c>
       <c r="G63">
-        <v>-10.89890770649004</v>
+        <v>-17.31169266944242</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.16434135137835</v>
       </c>
       <c r="E64">
-        <v>-13.28812525264111</v>
+        <v>-26.01807325086317</v>
       </c>
       <c r="F64">
-        <v>0.07300055849160147</v>
+        <v>-3.072018056244933</v>
       </c>
       <c r="G64">
-        <v>-11.33839124094051</v>
+        <v>-16.49050627159253</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.18583355132882</v>
       </c>
       <c r="E65">
-        <v>-13.1405830409972</v>
+        <v>-26.15244213161877</v>
       </c>
       <c r="F65">
-        <v>-0.09872414594575003</v>
+        <v>-3.194071366108218</v>
       </c>
       <c r="G65">
-        <v>-10.36916432938237</v>
+        <v>-16.8292759914974</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.17879827796799</v>
       </c>
       <c r="E66">
-        <v>-12.76636353442534</v>
+        <v>-26.05038844138191</v>
       </c>
       <c r="F66">
-        <v>-0.2051088863850822</v>
+        <v>-3.216906970301192</v>
       </c>
       <c r="G66">
-        <v>-11.3121053750278</v>
+        <v>-16.03199165209729</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.14379377574883</v>
       </c>
       <c r="E67">
-        <v>-12.77213733878512</v>
+        <v>-26.03468369352331</v>
       </c>
       <c r="F67">
-        <v>-0.306177164833247</v>
+        <v>-3.145976354701678</v>
       </c>
       <c r="G67">
-        <v>-11.00774582561682</v>
+        <v>-16.84348204023902</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.08892994425674</v>
       </c>
       <c r="E68">
-        <v>-13.41448779135114</v>
+        <v>-26.93099549691349</v>
       </c>
       <c r="F68">
-        <v>-0.2468478347099408</v>
+        <v>-3.178730830175774</v>
       </c>
       <c r="G68">
-        <v>-11.30949680388804</v>
+        <v>-16.80784141166033</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.01173948728155</v>
       </c>
       <c r="E69">
-        <v>-12.4618779990976</v>
+        <v>-25.94107560731075</v>
       </c>
       <c r="F69">
-        <v>-0.3751445496881254</v>
+        <v>-3.236533479175721</v>
       </c>
       <c r="G69">
-        <v>-11.43604039454958</v>
+        <v>-16.55555648900852</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.91524071570783</v>
       </c>
       <c r="E70">
-        <v>-12.64922096879493</v>
+        <v>-26.04217378953199</v>
       </c>
       <c r="F70">
-        <v>-0.2972423940266515</v>
+        <v>-3.412730539220787</v>
       </c>
       <c r="G70">
-        <v>-10.69143934850791</v>
+        <v>-16.34373723123857</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.800939056575999</v>
       </c>
       <c r="E71">
-        <v>-12.62303733208258</v>
+        <v>-26.15504147569917</v>
       </c>
       <c r="F71">
-        <v>-0.4256128337036854</v>
+        <v>-3.540970096848178</v>
       </c>
       <c r="G71">
-        <v>-10.91737114020504</v>
+        <v>-16.28050809178807</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.670941322750348</v>
       </c>
       <c r="E72">
-        <v>-12.89431103903806</v>
+        <v>-26.2094918471674</v>
       </c>
       <c r="F72">
-        <v>-0.5248678159071221</v>
+        <v>-3.775947279428494</v>
       </c>
       <c r="G72">
-        <v>-10.97451033244121</v>
+        <v>-16.32258319584483</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.524177076954613</v>
       </c>
       <c r="E73">
-        <v>-13.53595504965888</v>
+        <v>-26.50219429312718</v>
       </c>
       <c r="F73">
-        <v>-0.6189653826607291</v>
+        <v>-3.402374289950987</v>
       </c>
       <c r="G73">
-        <v>-10.62809208508127</v>
+        <v>-16.2334258436316</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.358679557370824</v>
       </c>
       <c r="E74">
-        <v>-13.45479121001941</v>
+        <v>-26.76778023672903</v>
       </c>
       <c r="F74">
-        <v>-0.615214535060853</v>
+        <v>-3.576089561257266</v>
       </c>
       <c r="G74">
-        <v>-11.12907227399885</v>
+        <v>-15.65032324152424</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.179905885395177</v>
       </c>
       <c r="E75">
-        <v>-13.23391941876929</v>
+        <v>-26.09590866210701</v>
       </c>
       <c r="F75">
-        <v>-0.6575623334267693</v>
+        <v>-3.655503487428849</v>
       </c>
       <c r="G75">
-        <v>-10.59491565389373</v>
+        <v>-15.82494164986399</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.984777086302147</v>
       </c>
       <c r="E76">
-        <v>-14.34824554631075</v>
+        <v>-26.22031490004573</v>
       </c>
       <c r="F76">
-        <v>-0.7206102048212425</v>
+        <v>-4.072123417360235</v>
       </c>
       <c r="G76">
-        <v>-10.05570923380862</v>
+        <v>-15.57122447400148</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.775839365359692</v>
       </c>
       <c r="E77">
-        <v>-14.63863394205261</v>
+        <v>-26.80993580126643</v>
       </c>
       <c r="F77">
-        <v>-0.5239499848248202</v>
+        <v>-3.424375728169342</v>
       </c>
       <c r="G77">
-        <v>-9.848847901814986</v>
+        <v>-15.74250095818294</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.551109502623673</v>
       </c>
       <c r="E78">
-        <v>-14.54767501313454</v>
+        <v>-26.46523741675058</v>
       </c>
       <c r="F78">
-        <v>-0.7233189662283969</v>
+        <v>-3.951408749219874</v>
       </c>
       <c r="G78">
-        <v>-9.892655490855132</v>
+        <v>-15.34221653709238</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.31775586423054</v>
       </c>
       <c r="E79">
-        <v>-15.44539970041511</v>
+        <v>-28.33763915012407</v>
       </c>
       <c r="F79">
-        <v>-0.9721679893359936</v>
+        <v>-3.747821721001243</v>
       </c>
       <c r="G79">
-        <v>-9.436772411050562</v>
+        <v>-14.86411958733037</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.074271600343492</v>
       </c>
       <c r="E80">
-        <v>-15.95926828843551</v>
+        <v>-27.54568150176664</v>
       </c>
       <c r="F80">
-        <v>-0.6772045812819512</v>
+        <v>-3.964878831556797</v>
       </c>
       <c r="G80">
-        <v>-9.140386230029039</v>
+        <v>-15.18305760412995</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.821215793590792</v>
       </c>
       <c r="E81">
-        <v>-16.25119636533998</v>
+        <v>-27.73732199329725</v>
       </c>
       <c r="F81">
-        <v>-0.6644005063368792</v>
+        <v>-4.113702490776354</v>
       </c>
       <c r="G81">
-        <v>-9.038779923219275</v>
+        <v>-14.6648821736301</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.563541812254082</v>
       </c>
       <c r="E82">
-        <v>-16.69182141476031</v>
+        <v>-28.60684787293205</v>
       </c>
       <c r="F82">
-        <v>-0.6971044513994037</v>
+        <v>-4.187904329249521</v>
       </c>
       <c r="G82">
-        <v>-8.74932040090974</v>
+        <v>-14.09072254088301</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.303924146872988</v>
       </c>
       <c r="E83">
-        <v>-16.84466194099319</v>
+        <v>-28.98617549818456</v>
       </c>
       <c r="F83">
-        <v>-0.8412793127544492</v>
+        <v>-4.173581856855119</v>
       </c>
       <c r="G83">
-        <v>-8.258439811952131</v>
+        <v>-13.96724689237955</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.044936022433832</v>
       </c>
       <c r="E84">
-        <v>-18.27100898461115</v>
+        <v>-30.05393306326814</v>
       </c>
       <c r="F84">
-        <v>-0.7060789838413335</v>
+        <v>-4.017003850377955</v>
       </c>
       <c r="G84">
-        <v>-7.670874748523926</v>
+        <v>-13.63714944105629</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.785637197803182</v>
       </c>
       <c r="E85">
-        <v>-19.68999272949263</v>
+        <v>-31.18491038973579</v>
       </c>
       <c r="F85">
-        <v>-0.8205659858474477</v>
+        <v>-4.201936873052945</v>
       </c>
       <c r="G85">
-        <v>-7.484370115085088</v>
+        <v>-13.40609566250487</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.534406355859299</v>
       </c>
       <c r="E86">
-        <v>-20.83287088565244</v>
+        <v>-31.09000715995705</v>
       </c>
       <c r="F86">
-        <v>-0.9773701366255745</v>
+        <v>-4.3188029462399</v>
       </c>
       <c r="G86">
-        <v>-7.587023131572317</v>
+        <v>-13.56297086526192</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.291156723482386</v>
       </c>
       <c r="E87">
-        <v>-22.1406670082236</v>
+        <v>-32.1697380103169</v>
       </c>
       <c r="F87">
-        <v>-0.7844806450466956</v>
+        <v>-4.261420279513173</v>
       </c>
       <c r="G87">
-        <v>-7.238777243803771</v>
+        <v>-14.04668362572292</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.059280836939785</v>
       </c>
       <c r="E88">
-        <v>-22.67403067684701</v>
+        <v>-33.43365321975373</v>
       </c>
       <c r="F88">
-        <v>-0.66773551350055</v>
+        <v>-4.12331238101623</v>
       </c>
       <c r="G88">
-        <v>-7.286161364343712</v>
+        <v>-12.99436470000419</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.842196041492805</v>
       </c>
       <c r="E89">
-        <v>-24.25167856553524</v>
+        <v>-34.73164293186127</v>
       </c>
       <c r="F89">
-        <v>-0.93858845992871</v>
+        <v>-4.340247721563573</v>
       </c>
       <c r="G89">
-        <v>-6.395877362284256</v>
+        <v>-13.27042371346495</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.645891676354514</v>
       </c>
       <c r="E90">
-        <v>-24.97997039781883</v>
+        <v>-36.71353184555521</v>
       </c>
       <c r="F90">
-        <v>-0.999240692794287</v>
+        <v>-4.634560861206418</v>
       </c>
       <c r="G90">
-        <v>-6.341251585762619</v>
+        <v>-13.0302382953136</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.471565594061852</v>
       </c>
       <c r="E91">
-        <v>-27.02592589753628</v>
+        <v>-36.64684553731826</v>
       </c>
       <c r="F91">
-        <v>-1.138999527525008</v>
+        <v>-4.796226700271575</v>
       </c>
       <c r="G91">
-        <v>-6.549924152057065</v>
+        <v>-13.02055212927011</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.319012024100966</v>
       </c>
       <c r="E92">
-        <v>-28.69528897030186</v>
+        <v>-37.44072099441792</v>
       </c>
       <c r="F92">
-        <v>-1.049453839649785</v>
+        <v>-4.587874074384638</v>
       </c>
       <c r="G92">
-        <v>-6.902757187565715</v>
+        <v>-12.69857898252804</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.192795008809774</v>
       </c>
       <c r="E93">
-        <v>-30.89111431730316</v>
+        <v>-39.27146303115785</v>
       </c>
       <c r="F93">
-        <v>-1.083696062979308</v>
+        <v>-4.772244635593127</v>
       </c>
       <c r="G93">
-        <v>-6.435314364207222</v>
+        <v>-12.96140482943956</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.089669003445131</v>
       </c>
       <c r="E94">
-        <v>-32.05421890261823</v>
+        <v>-40.94675614063647</v>
       </c>
       <c r="F94">
-        <v>-1.37112298440268</v>
+        <v>-4.984003508240376</v>
       </c>
       <c r="G94">
-        <v>-7.061715966013015</v>
+        <v>-13.31885126246079</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.008553705444392</v>
       </c>
       <c r="E95">
-        <v>-33.92105514143629</v>
+        <v>-42.60720491231795</v>
       </c>
       <c r="F95">
-        <v>-1.346497278252257</v>
+        <v>-4.979293411188058</v>
       </c>
       <c r="G95">
-        <v>-6.354596313844882</v>
+        <v>-13.64048644338224</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.944033292081212</v>
       </c>
       <c r="E96">
-        <v>-35.41159103987597</v>
+        <v>-44.01067863372316</v>
       </c>
       <c r="F96">
-        <v>-1.301135050907553</v>
+        <v>-5.036311596257553</v>
       </c>
       <c r="G96">
-        <v>-6.657656499518314</v>
+        <v>-13.62015271337836</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.89490363009832</v>
       </c>
       <c r="E97">
-        <v>-37.73510576847156</v>
+        <v>-45.68957188003788</v>
       </c>
       <c r="F97">
-        <v>-1.516787250347959</v>
+        <v>-5.123447563358033</v>
       </c>
       <c r="G97">
-        <v>-7.728223938939901</v>
+        <v>-13.62877576363658</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.855406454803725</v>
       </c>
       <c r="E98">
-        <v>-39.75083596842481</v>
+        <v>-47.05606155422245</v>
       </c>
       <c r="F98">
-        <v>-1.449355658657871</v>
+        <v>-5.216925511294346</v>
       </c>
       <c r="G98">
-        <v>-7.017777128110491</v>
+        <v>-13.0809430120717</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.817269580557298</v>
       </c>
       <c r="E99">
-        <v>-42.31520437982935</v>
+        <v>-48.4948052954364</v>
       </c>
       <c r="F99">
-        <v>-1.502182304669201</v>
+        <v>-5.461375903493077</v>
       </c>
       <c r="G99">
-        <v>-7.551277503903726</v>
+        <v>-14.2400378091671</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.782234691447466</v>
       </c>
       <c r="E100">
-        <v>-43.93049973718036</v>
+        <v>-49.54249945642899</v>
       </c>
       <c r="F100">
-        <v>-1.694666724588111</v>
+        <v>-5.478142059725739</v>
       </c>
       <c r="G100">
-        <v>-7.556130430590144</v>
+        <v>-14.9140368109142</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.740879892970825</v>
       </c>
       <c r="E101">
-        <v>-46.31391032723839</v>
+        <v>-50.51424431560194</v>
       </c>
       <c r="F101">
-        <v>-2.092617738362605</v>
+        <v>-5.528031314926743</v>
       </c>
       <c r="G101">
-        <v>-7.881430735993494</v>
+        <v>-14.48349788643478</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.7043719851309</v>
       </c>
       <c r="E102">
-        <v>-48.39403769181772</v>
+        <v>-53.29657723794367</v>
       </c>
       <c r="F102">
-        <v>-1.941111825492784</v>
+        <v>-5.475219579528662</v>
       </c>
       <c r="G102">
-        <v>-8.259404491090608</v>
+        <v>-15.05732447519359</v>
       </c>
     </row>
   </sheetData>
